--- a/client-docs/test-cases/emg-o-test-cases-product-master-sales.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-product-master-sales.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Material เป็นโหมด Lot มี Bundle ที่มีสต็อกรวมเพียงพอ</t>
+          <t>Material เป็นโหมด Lot มี Block ที่มีสต็อกรวมเพียงพอ</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Bundle เป็นโหมด Lot อยู่ Empire Stone, SO เป็นของ Empire Granite ระบุจำนวนตร.ม.บางส่วน</t>
+          <t>Block เป็นโหมด Lot อยู่ Empire Stone, SO เป็นของ Empire Granite ระบุจำนวนตร.ม.บางส่วน</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Bundle/Block ทุกรายการใน SO อยู่บริษัทเดียวกับ SO เอง</t>
+          <t>Block ทุกรายการใน SO อยู่บริษัทเดียวกับ SO เอง</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2730,7 +2730,7 @@
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>1. Login ด้วยผู้ใช้นี้
-2. เปิดรายการ Stone Bundle/Slab</t>
+2. เปิดรายการ Stone Block/Slab</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2819,7 +2819,7 @@
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>1. Login ด้วยผู้ใช้นี้
-2. มองหาเมนู Stone Material/Bundle/Slab</t>
+2. มองหาเมนู Stone Material/Block/Slab</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>1. กรอก Flat Cost / Piece และ Flat Sale Price / Piece
-2. เปิด Bundle ของ Material นี้ &gt; แท็บ Slabs &gt; เพิ่ม 1 แถว
+2. เปิด Block ของ Material นี้ &gt; แท็บ Slabs &gt; เพิ่ม 1 แถว
 3. ตรวจ Cost ของแผ่นที่ได้ (คอลัมน์ Cost หรือเปิดแผ่นดู)</t>
         </is>
       </c>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle ของ Material นี้ &gt; แท็บ Slabs &gt; เพิ่ม 1 แถว ระบุ Slab L / Slab H
+          <t>1. เปิด Block ของ Material นี้ &gt; แท็บ Slabs &gt; เพิ่ม 1 แถว ระบุ Slab L / Slab H
 2. ตรวจ Cost ของแผ่นที่ได้</t>
         </is>
       </c>
@@ -3759,7 +3759,7 @@
         <is>
           <t>Slab L (M) = 2.0
 Slab H (M) = 1.5
-Cost / Sq.Mt. ของ Bundle = 1,000</t>
+Cost / Sq.Mt. ของ Block = 1,000</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle &gt; แท็บ Slabs &gt; เพิ่ม 1 แถว ระบุ Slab L / Slab H
+          <t>1. เปิด Block &gt; แท็บ Slabs &gt; เพิ่ม 1 แถว ระบุ Slab L / Slab H
 2. ตรวจ Cost ของแผ่นที่ได้</t>
         </is>
       </c>
@@ -3808,7 +3808,7 @@
         <is>
           <t>Slab L (M) = 2.0
 Slab H (M) = 1.5
-Cost / Sq.Mt. ของ Bundle = 1,000</t>
+Cost / Sq.Mt. ของ Block = 1,000</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>A5. Finish / Variant Resolution — ADR-018 — Finish ของ Bundle เป็นตัวกำหนด Variant ที่ใช้ตัด/ผลิต</t>
+          <t>A5. Finish / Variant Resolution — ADR-018 — Finish ของ Block เป็นตัวกำหนด Variant ที่ใช้ตัด/ผลิต</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle (Block/Lot) ของ Material นี้
+          <t>1. เปิด Block ของ Material นี้
 2. ลองตั้งค่า Finish เป็นค่าใดก็ได้ (หรือปล่อยว่าง)
 3. ไปแท็บ Slabs เพิ่ม 1 แถว หรือกด "Create Cut Order"</t>
         </is>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle ของ Material นี้
+          <t>1. เปิด Block ของ Material นี้
 2. ตั้งค่า Finish = "Polished"
 3. ไปแท็บ Slabs เพิ่ม 1 แถว หรือกด "Create Cut Order" แล้วยืนยัน MO</t>
         </is>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle ของ Material นี้
+          <t>1. เปิด Block ของ Material นี้
 2. ปล่อยช่อง Finish ว่างไว้ (ไม่เลือก)
 3. ไปแท็บ Slabs ลองเพิ่มแถวแรก</t>
         </is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle ของ Material นี้ กด "Create Cut Order" (หรือกด "Cut to Order" จาก SO line)
+          <t>1. เปิด Block ของ Material นี้ กด "Create Cut Order" (หรือกด "Cut to Order" จาก SO line)
 2. กรอกฟิลด์ในหน้าต่าง "Create Cut Order"
 3. ตรวจ Manufacturing &gt; Work Centers และ Bill of Materials</t>
         </is>
@@ -4517,7 +4517,7 @@
         <is>
           <t>Target L (M) = 2.0
 Target H (M) = 1.2
-Cut From Block = เลือก Bundle ที่มีอยู่ (เช่น BDL-00002)</t>
+Cut From Block = เลือก Block ที่มีอยู่ (เช่น BLK-26-0002)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle ของ Material นี้ &gt; แท็บ Slabs &gt; กด "Add a line" กรอก Slab L / Slab H แล้วบันทึก
+          <t>1. เปิด Block ของ Material นี้ &gt; แท็บ Slabs &gt; กด "Add a line" กรอก Slab L / Slab H แล้วบันทึก
 2. เปิดเมนู Slabs (เมนูบนสุด) หาแผ่นที่เพิ่งเพิ่มไป เปิดดู</t>
         </is>
       </c>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Bundle ของ Material นี้ &gt; แท็บ Slabs &gt; กด "Add a line"
+          <t>1. เปิด Block ของ Material นี้ &gt; แท็บ Slabs &gt; กด "Add a line"
 2. เปิดเมนู Slabs หาแผ่นที่ได้ เปิดดู Total Cost</t>
         </is>
       </c>
